--- a/CBT_2022_2회/산업안전기사_2022_2회_문항등록.xlsx
+++ b/CBT_2022_2회/산업안전기사_2022_2회_문항등록.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1592,17 +1592,17 @@
       </c>
       <c r="AG4" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;훈련에만 전념할 수 있는&lt;/strong&gt; 것이 Off JT 의 장점이다. 나머지 셋은 &lt;strong&gt;OJT&lt;/strong&gt;의 장점이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;OJT 와 Off JT&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;OJT&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;Off JT&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;어디서&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;일하는 자리에서&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;따로 자리를 마련해&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;장점&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;현장 실정에 맞다 · 개별 지도 · 상호 신뢰가 두터워진다 · 업무의 지속성이 유지된다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;훈련에만 전념할 수 있다 · 여럿을 한꺼번에 · 전문 강사 · 여러 매체 · 다른 곳의 사례를 배운다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;단점&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전문성이 낮다 · 여럿을 못 가르친다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;현장과 동떨어질 수 있다 · 업무가 비게 된다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;훈련에만 전념할 수 있는&lt;/strong&gt; 것이 Off JT의 장점이다. 나머지 셋은 &lt;strong&gt;OJT&lt;/strong&gt;의 장점이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;OJT와 Off JT&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;OJT&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;Off JT&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;어디서&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;일하는 자리에서&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;따로 자리를 마련해&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;장점&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;현장 실정에 맞다 · 개별 지도 · 상호 신뢰가 두터워진다 · 업무의 지속성이 유지된다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;훈련에만 전념할 수 있다 · 여럿을 한꺼번에 · 전문 강사 · 여러 매체 · 다른 곳의 사례를 배운다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;단점&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전문성이 낮다 · 여럿을 못 가르친다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;현장과 동떨어질 수 있다 · 업무가 비게 된다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH4" s="32" t="inlineStr">
         <is>
-          <t>② 상호 신뢰와 이해도가 높아지는 것은 OJT 의 장점이다.&lt;br&gt;③ 개개인에 맞춘 지도훈련이 가능한 것도 그렇다.&lt;br&gt;④ 직장 실정에 맞는 실제적 훈련이 가능한 것도 그렇다.</t>
+          <t>② 상호 신뢰와 이해도가 높아지는 것은 OJT의 장점이다.&lt;br&gt;③ 개개인에 맞춘 지도훈련이 가능한 것도 그렇다.&lt;br&gt;④ 직장 실정에 맞는 실제적 훈련이 가능한 것도 그렇다.</t>
         </is>
       </c>
       <c r="AI4" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;OJT 와 Off JT&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「일을 놓고(off) 배운다」&lt;/strong&gt;는 이름 그대로 &lt;strong&gt;훈련에만 매달릴 수 있는 것&lt;/strong&gt;이 Off JT 의 본질이다. &lt;strong&gt;현장 · 상사 · 개별이라는 낱말이 붙으면 OJT&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;훈련에만 전념하면 Off JT&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;OJT와 Off JT&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「일을 놓고(off) 배운다」&lt;/strong&gt;는 이름 그대로 &lt;strong&gt;훈련에만 매달릴 수 있는 것&lt;/strong&gt;이 Off JT의 본질이다. &lt;strong&gt;현장 · 상사 · 개별이라는 낱말이 붙으면 OJT&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;훈련에만 전념하면 Off JT&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="AI6" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;유해작업의 근로시간 제한&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「6과 34」&lt;/strong&gt; 한 짝이다 — &lt;strong&gt;6 × 5일 = 30 이 아니라 34&lt;/strong&gt;라는 점이 눈에 걸린다. &lt;strong&gt;일반 근로시간 「8과 40」과 나란히&lt;/strong&gt; 놓아 외운다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;1일 6시간, 1주 34시간&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;유해작업의 근로시간 제한&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「6과 34」&lt;/strong&gt;한 짝이다 — &lt;strong&gt;6 × 5일 = 30이 아니라 34&lt;/strong&gt;라는 점이 눈에 걸린다. &lt;strong&gt;일반 근로시간 「8과 40」과 나란히&lt;/strong&gt; 놓아 외운다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;1일 6시간, 1주 34시간&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="AG12" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건개선계획을 수립&lt;/strong&gt; 하여 제출하도록 명할 수 있다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전보건개선계획 수립 대상 사업장&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대상&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;산업재해율이 같은 업종 평균 재해율보다 높은 사업장&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사업주가 안전보건조치 의무를 이행하지 않아 중대재해가 발생한 사업장&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;직업성 질병자가 연간 2명 이상(상시근로자 1천 명 이상은 3명 이상) 발생한 사업장&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;유해인자의 노출기준을 초과한 사업장&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;제출 기한&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;명령을 받은 날부터 60일 이내&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건개선계획을 수립&lt;/strong&gt;하여 제출하도록 명할 수 있다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전보건개선계획 수립 대상 사업장&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대상&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;산업재해율이 같은 업종 평균 재해율보다 높은 사업장&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사업주가 안전보건조치 의무를 이행하지 않아 중대재해가 발생한 사업장&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;직업성 질병자가 연간 2명 이상(상시근로자 1천 명 이상은 3명 이상) 발생한 사업장&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;유해인자의 노출기준을 초과한 사업장&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;제출 기한&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;명령을 받은 날부터 60일 이내&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH12" s="32" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="AG17" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;남의 생각에 얹어 고쳐 내는 것(수정발언)&lt;/strong&gt;은 오히려 &lt;strong&gt;권장&lt;/strong&gt; 된다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;브레인스토밍의 4원칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;원칙&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비판금지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;남의 의견을 평가하지 않는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;자유분방&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;마음대로 이야기한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;①&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대량발언&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사소해도 되도록 많이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;③&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수정발언&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;남의 의견에 얹어 고쳐 낸다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;④가 이것을 막고 있다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;남의 생각에 얹어 고쳐 내는 것(수정발언)&lt;/strong&gt;은 오히려 &lt;strong&gt;권장&lt;/strong&gt;된다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;브레인스토밍의 4원칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;원칙&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비판금지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;남의 의견을 평가하지 않는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;자유분방&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;마음대로 이야기한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;①&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대량발언&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사소해도 되도록 많이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;③&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수정발언&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;남의 의견에 얹어 고쳐 낸다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;④가 이것을 막고 있다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH17" s="32" t="inlineStr">
@@ -3644,17 +3644,17 @@
       </c>
       <c r="AG20" s="32" t="inlineStr">
         <is>
-          <t>$\text{도수율} = \dfrac{\text{연천인율}}{2.4} = \dfrac{7}{2.4} \fallingdotseq 2.92$ 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;연천인율과 도수율&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연천인율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{연간 재해자수}}{\text{연평균 근로자수}} \times 1 {,} 000$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;도수율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{재해건수}}{\text{연근로시간수}} \times 10^{6}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;관계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;연천인율 = 도수율 × 2.4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1인이 연 2,400시간 근무한다고 볼 때&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;7 ÷ 2.4 = 2.92&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$\text{도수율} = \dfrac{\text{연천인율}}{2.4} = \dfrac{7}{2.4} \fallingdotseq 2.92$다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;연천인율과 도수율&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연천인율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{연간 재해자수}}{\text{연평균 근로자수}} \times 1 {,} 000$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;도수율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{재해건수}}{\text{연근로시간수}} \times 10^{6}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;관계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;연천인율 = 도수율 × 2.4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1인이 연 2,400시간 근무한다고 볼 때&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;7 ÷ 2.4 = 2.92&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH20" s="32" t="inlineStr">
         <is>
-          <t>① 2.41 은 계산과 맞지 않는다.&lt;br&gt;③ 3.42 도 그렇다.&lt;br&gt;④ 4.53 도 그렇다.</t>
+          <t>① 2.41은 계산과 맞지 않는다.&lt;br&gt;③ 3.42 도 그렇다.&lt;br&gt;④ 4.53 도 그렇다.</t>
         </is>
       </c>
       <c r="AI20" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;연천인율과 도수율&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;2.4 라는 수는 「1인 연간 2,400시간」&lt;/strong&gt;에서 나온다 — &lt;strong&gt;이 문항의 8 × 300 = 2,400 시간이 바로 그것&lt;/strong&gt;이다. &lt;strong&gt;연천인율이 도수율보다 크므로 나눈다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;연천인율 = 도수율 × 2.4&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;연천인율과 도수율&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;2.4라는 수는 「1인 연간 2,400시간」&lt;/strong&gt;에서 나온다 — &lt;strong&gt;이 문항의 8 × 300 = 2,400 시간이 바로 그것&lt;/strong&gt;이다. &lt;strong&gt;연천인율이 도수율보다 크므로 나눈다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;연천인율 = 도수율 × 2.4&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="AI23" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;미니멀 컷셋과 위험수준&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「길이 많을수록」과 「길이 짧을수록」 위험&lt;/strong&gt; 하다 — &lt;strong&gt;컷셋의 수도, 컷셋 안 사상의 적음도 모두 위험을 키운다&lt;/strong&gt;. &lt;strong&gt;④는 그 둘째를 뒤집어&lt;/strong&gt; 놓았다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;컷셋이 많고 짧을수록 위험&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;미니멀 컷셋과 위험수준&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「길이 많을수록」과 「길이 짧을수록」 위험&lt;/strong&gt;하다 — &lt;strong&gt;컷셋의 수도, 컷셋 안 사상의 적음도 모두 위험을 키운다&lt;/strong&gt;. &lt;strong&gt;④는 그 둘째를 뒤집어&lt;/strong&gt; 놓았다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;컷셋이 많고 짧을수록 위험&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4294,7 +4294,7 @@
       </c>
       <c r="AH25" s="32" t="inlineStr">
         <is>
-          <t>① 시스템의 약점을 나타내는 것은 컷셋이다.&lt;br&gt;② 정상사상을 일으키는 조합도 컷셋이다.&lt;br&gt;④ Fussell Algorithm 은 컷셋을 구할 때 쓴다.</t>
+          <t>① 시스템의 약점을 나타내는 것은 컷셋이다.&lt;br&gt;② 정상사상을 일으키는 조합도 컷셋이다.&lt;br&gt;④ Fussell Algorithm은 컷셋을 구할 때 쓴다.</t>
         </is>
       </c>
       <c r="AI25" s="32" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="AG27" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;직접조명&lt;/strong&gt;이다. &lt;strong&gt;빛이 곧바로 내리쬐어 그림자가 짙게&lt;/strong&gt; 진다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;조명방법&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;방법&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;직접조명&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;빛의 90 ~ 100% 를 아래로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;효율이 높다 / 그림자가 짙고 눈부시다&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;반직접조명&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;60 ~ 90% 를 아래로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전반확산조명&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;고루 퍼뜨린다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;반간접조명&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;60 ~ 90% 를 위로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;간접조명&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;90 ~ 100% 를 위로 보내 천장에 반사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;그림자가 없고 눈이 편하다 / 효율이 낮다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;직접조명&lt;/strong&gt;이다. &lt;strong&gt;빛이 곧바로 내리쬐어 그림자가 짙게&lt;/strong&gt; 진다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;조명방법&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;방법&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;직접조명&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;빛의 90 ~ 100%를 아래로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;효율이 높다 / 그림자가 짙고 눈부시다&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;반직접조명&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;60 ~ 90%를 아래로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전반확산조명&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;고루 퍼뜨린다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;반간접조명&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;60 ~ 90%를 위로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;간접조명&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;90 ~ 100%를 위로 보내 천장에 반사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;그림자가 없고 눈이 편하다 / 효율이 낮다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH27" s="32" t="inlineStr">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="AI31" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;예비위험분석(PHA)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;PHA 는 「아직 설계도 없는 때에 무엇이 위험할까」&lt;/strong&gt;를 먼저 훑는 것이다 — &lt;strong&gt;그래서 맨 처음인 구상단계&lt;/strong&gt;다. &lt;strong&gt;위험을 파국적 · 위기적 · 한계적 · 무시가능 네 등급&lt;/strong&gt;으로 나눈다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;PHA 는 구상단계&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;예비위험분석(PHA)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;PHA는 「아직 설계도 없는 때에 무엇이 위험할까」&lt;/strong&gt;를 먼저 훑는 것이다 — &lt;strong&gt;그래서 맨 처음인 구상단계&lt;/strong&gt;다. &lt;strong&gt;위험을 파국적 · 위기적 · 한계적 · 무시가능 네 등급&lt;/strong&gt;으로 나눈다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;PHA는 구상단계&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="AG33" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;MTBF 는 「평균 고장률」이 아니라 「평균 고장간격」&lt;/strong&gt;이다. &lt;strong&gt;고장률과는 반비례(&lt;/strong&gt;$\mathrm{MTBF} = 1 / \lambda$&lt;strong&gt;)&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;수명과 신뢰성&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;MTBF&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;평균 고장간격&lt;/u&gt; — 고장률 $\lambda$ 의 역수 · 「평균 고장률」이 아니다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;직렬 시스템&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가장 짧은 수명의 부품이 전체 수명을 정한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;병렬(리던던시)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;중복도가 늘수록 수명이 길어진다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;디레이팅&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정격보다 낮춰 쓴다&lt;/u&gt; — 신뢰성이 올라간다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;MTBF는 「평균 고장률」이 아니라 「평균 고장간격」&lt;/strong&gt;이다. &lt;strong&gt;고장률과는 반비례(&lt;/strong&gt;$\mathrm{MTBF} = 1 / \lambda$&lt;strong&gt;)&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;수명과 신뢰성&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;MTBF&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;평균 고장간격&lt;/u&gt; — 고장률 $\lambda$의 역수 · 「평균 고장률」이 아니다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;직렬 시스템&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가장 짧은 수명의 부품이 전체 수명을 정한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;병렬(리던던시)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;중복도가 늘수록 수명이 길어진다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;디레이팅&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정격보다 낮춰 쓴다&lt;/u&gt; — 신뢰성이 올라간다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH33" s="32" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="AI33" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;MTBF 와 고장률&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;MTBF(Mean Time Between Failures)는 「시간」이지 「률」이 아니다&lt;/strong&gt; — &lt;strong&gt;보기가 그 이름을 「평균 고장율」로 바꿔 놓았고, 관계도 비례가 아니라 반비례&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $\mathrm{MTBF} = 1 / \lambda$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;MTBF와 고장률&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;MTBF(Mean Time Between Failures)는 「시간」이지 「률」이 아니다&lt;/strong&gt; — &lt;strong&gt;보기가 그 이름을 「평균 고장율」로 바꿔 놓았고, 관계도 비례가 아니라 반비례&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $\mathrm{MTBF} = 1 / \lambda$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="AG36" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;분자량&lt;/strong&gt;은 열교환 경로가 아니다. 경로는 &lt;strong&gt;전도 · 대류 · 복사 · 증발&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;인체의 열교환&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;경로&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전도(conduction)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;맞닿은 물체로 곧장&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대류(convection)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;공기의 흐름을 타고&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;복사(radiation)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전자기파로 곧바로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;증발(evaporation)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;땀이 마르며 열을 빼앗는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;더울 때 가장 중요&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;열균형 방정식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$S = M - E \pm R \pm C - W$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;S 는 축적, M 은 대사, W 는 한 일&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;분자량&lt;/strong&gt;은 열교환 경로가 아니다. 경로는 &lt;strong&gt;전도 · 대류 · 복사 · 증발&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;인체의 열교환&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;경로&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전도(conduction)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;맞닿은 물체로 곧장&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대류(convection)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;공기의 흐름을 타고&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;복사(radiation)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전자기파로 곧바로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;증발(evaporation)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;땀이 마르며 열을 빼앗는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;더울 때 가장 중요&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;열균형 방정식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$S = M - E \pm R \pm C - W$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;S는 축적, M은 대사, W는 한 일&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH36" s="32" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="AH37" s="32" t="inlineStr">
         <is>
-          <t>① 500 ~ 1,000 [Hz] 는 회화음역이라 나중에 나빠진다.&lt;br&gt;③ 8,000 ~ 10,000 [Hz] 는 시작 대역이 아니다.&lt;br&gt;④ 15,000 ~ 20,000 [Hz] 는 가청 범위의 끝이다.</t>
+          <t>① 500 ~ 1,000 [Hz]는 회화음역이라 나중에 나빠진다.&lt;br&gt;③ 8,000 ~ 10,000 [Hz]는 시작 대역이 아니다.&lt;br&gt;④ 15,000 ~ 20,000 [Hz]는 가청 범위의 끝이다.</t>
         </is>
       </c>
       <c r="AI37" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;소음성 난청&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;4,000 [Hz] 부터 파이므로 초기에는 본인이 알아채지 못한다&lt;/strong&gt; — &lt;strong&gt;말소리는 500 ~ 2,000 [Hz] 라 대화에 지장이 없기&lt;/strong&gt; 때문이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;소음성 난청은 4,000 [Hz] 언저리&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;소음성 난청&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;4,000 [Hz]부터 파이므로 초기에는 본인이 알아채지 못한다&lt;/strong&gt; — &lt;strong&gt;말소리는 500 ~ 2,000 [Hz] 라 대화에 지장이 없기&lt;/strong&gt; 때문이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;소음성 난청은 4,000 [Hz] 언저리&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6068,12 +6068,12 @@
       </c>
       <c r="AH39" s="32" t="inlineStr">
         <is>
-          <t>② FHA 는 정성적 기법이다.&lt;br&gt;③ PHA 도 정성적이다.&lt;br&gt;④ FMEA 도 정성적이다.</t>
+          <t>② FHA는 정성적 기법이다.&lt;br&gt;③ PHA 도 정성적이다.&lt;br&gt;④ FMEA 도 정성적이다.</t>
         </is>
       </c>
       <c r="AI39" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;위험분석 기법의 정성·정량&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;정량적인 것은 ETA 와 FTA 둘뿐&lt;/strong&gt;이다 — &lt;strong&gt;둘 다 확률을 셈하며, ETA 는 원인에서 결과로(귀납), FTA 는 결과에서 원인으로(연역)&lt;/strong&gt; 간다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;정량적은 ETA 와 FTA&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;위험분석 기법의 정성·정량&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;정량적인 것은 ETA와 FTA 둘뿐&lt;/strong&gt;이다 — &lt;strong&gt;둘 다 확률을 셈하며, ETA는 원인에서 결과로(귀납), FTA는 결과에서 원인으로(연역)&lt;/strong&gt; 간다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;정량적은 ETA와 FTA&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="AG40" s="32" t="inlineStr">
         <is>
-          <t>FTA 는 &lt;strong&gt;톱다운(Top-Down)&lt;/strong&gt; 방식이다. &lt;strong&gt;정상사상에서 아래로 내려가며 원인을 찾는다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA 와 FMEA&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;FTA&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;FMEA&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;방향&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Top-Down(하향식)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Bottom-Up(상향식)&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;논리&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;연역적&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;귀납적&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;출발점&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정상사상(결과)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;부품(원인)&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;정량화&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;자료가 쌓이면 가능&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;어렵다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;잘 맞는 것&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;기능적 결함의 원인 분석&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;부품의 고장 영향&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>FTA는 &lt;strong&gt;톱다운(Top-Down)&lt;/strong&gt; 방식이다. &lt;strong&gt;정상사상에서 아래로 내려가며 원인을 찾는다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA와 FMEA&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;FTA&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;FMEA&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;방향&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Top-Down(하향식)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Bottom-Up(상향식)&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;논리&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;연역적&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;귀납적&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;출발점&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정상사상(결과)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;부품(원인)&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;정량화&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;자료가 쌓이면 가능&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;어렵다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;잘 맞는 것&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;기능적 결함의 원인 분석&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;부품의 고장 영향&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH40" s="32" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="AI40" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FTA 의 특징&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;나무는 위에서 아래로 가지를 뻗는다&lt;/strong&gt; — &lt;strong&gt;FTA 는 정상사상이라는 뿌리(꼭대기)에서 시작하므로 Top-Down&lt;/strong&gt;이다. &lt;strong&gt;연역적이라는 말과 짝&lt;/strong&gt;이 맞아야 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;FTA 는 Top-Down&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FTA의 특징&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;나무는 위에서 아래로 가지를 뻗는다&lt;/strong&gt; — &lt;strong&gt;FTA는 정상사상이라는 뿌리(꼭대기)에서 시작하므로 Top-Down&lt;/strong&gt;이다. &lt;strong&gt;연역적이라는 말과 짝&lt;/strong&gt;이 맞아야 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;FTA는 Top-Down&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6321,17 +6321,17 @@
       </c>
       <c r="AG41" s="32" t="inlineStr">
         <is>
-          <t>추천값 0.13 [cm] 는 &lt;strong&gt;시거리 71 [cm]&lt;/strong&gt; 기준이다. $\dfrac{142}{71} = 2$ 배이므로 $0.13 \times 2 = 0.26$ [cm] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;시거리와 눈금 간격&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기준&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시거리 71 [cm] 에서 눈금 간격 0.13 [cm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;관계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시거리에 비례한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;멀어지면 그만큼 넓혀야 보인다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;142 ÷ 71 = 2 배 → 0.26 [cm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>추천값 0.13 [cm]는 &lt;strong&gt;시거리 71 [cm]&lt;/strong&gt; 기준이다. $\dfrac{142}{71} = 2$ 배이므로 $0.13 \times 2 = 0.26$ [cm]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;시거리와 눈금 간격&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기준&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시거리 71 [cm]에서 눈금 간격 0.13 [cm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;관계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시거리에 비례한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;멀어지면 그만큼 넓혀야 보인다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;142 ÷ 71 = 2 배 → 0.26 [cm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH41" s="32" t="inlineStr">
         <is>
-          <t>① 0.065 [cm] 는 오히려 절반으로 줄인 값이다.&lt;br&gt;② 0.13 [cm] 는 71 [cm] 기준의 값이다.&lt;br&gt;④ 0.39 [cm] 는 3배로 잡은 값이다.</t>
+          <t>① 0.065 [cm]는 오히려 절반으로 줄인 값이다.&lt;br&gt;② 0.13 [cm]는 71 [cm] 기준의 값이다.&lt;br&gt;④ 0.39 [cm]는 3배로 잡은 값이다.</t>
         </is>
       </c>
       <c r="AI41" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;정량적 표시장치의 눈금 간격&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;71 [cm] 라는 기준 시거리&lt;/strong&gt;를 알아야 풀린다 — &lt;strong&gt;142 가 그 두 배라는 것이 문제의 설계&lt;/strong&gt;다. &lt;strong&gt;멀어질수록 눈금을 넓혀야 같은 시각(視角)으로 보인다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;시거리 71 [cm] 에 0.13 [cm]&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;정량적 표시장치의 눈금 간격&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;71 [cm]라는 기준 시거리&lt;/strong&gt;를 알아야 풀린다 — &lt;strong&gt;142가 그 두 배라는 것이 문제의 설계&lt;/strong&gt;다. &lt;strong&gt;멀어질수록 눈금을 넓혀야 같은 시각(視角)으로 보인다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;시거리 71 [cm]에 0.13 [cm]&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6589,7 +6589,7 @@
       </c>
       <c r="AI43" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;밀링의 상향절삭과 하향절삭&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;하향절삭은 커터가 일감을 「끌어당기며」 깎으므로 테이블이 앞으로 딸려 간다&lt;/strong&gt; — &lt;strong&gt;그 틈(백래시)이 문제라 제거장치가 필요&lt;/strong&gt; 하다. &lt;strong&gt;상향절삭은 밀어내는 쪽이라 틈이 저절로 메워진다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;백래시 자연 제거는 상향절삭&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;밀링의 상향절삭과 하향절삭&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;하향절삭은 커터가 일감을 「끌어당기며」 깎으므로 테이블이 앞으로 딸려 간다&lt;/strong&gt; — &lt;strong&gt;그 틈(백래시)이 문제라 제거장치가 필요&lt;/strong&gt;하다. &lt;strong&gt;상향절삭은 밀어내는 쪽이라 틈이 저절로 메워진다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;백래시 자연 제거는 상향절삭&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6837,17 +6837,17 @@
       </c>
       <c r="AG45" s="32" t="inlineStr">
         <is>
-          <t>분할날의 최소길이는 $\dfrac{\pi D}{6} = \dfrac{\pi \times 500}{6} \fallingdotseq 262$ [mm] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;분할날의 치수&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;최소길이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\pi D}{6}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;톱날 원주의 1/6&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;톱날과의 간격&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;12 [mm] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;방호 범위&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;톱날 후면날의 2/3 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;두께&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;톱날 두께의 1.1배 이상, 치진폭보다 작을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>분할날의 최소길이는 $\dfrac{\pi D}{6} = \dfrac{\pi \times 500}{6} \fallingdotseq 262$ [mm]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;분할날의 치수&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;최소길이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\pi D}{6}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;톱날 원주의 1/6&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;톱날과의 간격&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;12 [mm] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;방호 범위&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;톱날 후면날의 2/3 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;두께&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;톱날 두께의 1.1배 이상, 치진폭보다 작을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH45" s="32" t="inlineStr">
         <is>
-          <t>② 314 [mm] 는 원주를 5로 나눈 값에 가깝다.&lt;br&gt;③ 333 [mm] 는 계산과 맞지 않는다.&lt;br&gt;④ 410 [mm] 도 그렇다.</t>
+          <t>② 314 [mm]는 원주를 5로 나눈 값에 가깝다.&lt;br&gt;③ 333 [mm]는 계산과 맞지 않는다.&lt;br&gt;④ 410 [mm] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI45" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;목재가공용 둥근톱의 분할날&lt;/strong&gt;&lt;br&gt;$\pi \times 500 = 1 {,} 571$ [mm] 가 원주이고 &lt;strong&gt;그 1/6 이 약 262 [mm]&lt;/strong&gt;다. &lt;strong&gt;「1/6」이라는 분수 하나면&lt;/strong&gt; 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $\dfrac{\pi D}{6}$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;목재가공용 둥근톱의 분할날&lt;/strong&gt;&lt;br&gt;$\pi \times 500 = 1 {,} 571$ [mm]가 원주이고 &lt;strong&gt;그 1/6이 약 262 [mm]&lt;/strong&gt;다. &lt;strong&gt;「1/6」이라는 분수 하나면&lt;/strong&gt; 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $\dfrac{\pi D}{6}$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7095,17 +7095,17 @@
       </c>
       <c r="AG47" s="32" t="inlineStr">
         <is>
-          <t>$D = 1 {,} 600 ( T_{c} + T_{s} ) = 1 {,} 600 \times ( 0.05 + 0.15 ) = 320$ [mm] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;광전자식 방호장치의 안전거리&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전거리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$D = 1 {,} 600 ( T_{c} + T_{s} )$ [mm]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;$T_{c}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;빛을 가린 뒤 급정지장치가 작동을 시작할 때까지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.05초&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;$T_{s}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;급정지장치가 작동해 슬라이드가 멈출 때까지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.15초&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1,600&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사람 손이 뻗는 속도 [mm/s]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$D = 1 {,} 600 ( T_{c} + T_{s} ) = 1 {,} 600 \times ( 0.05 + 0.15 ) = 320$ [mm]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;광전자식 방호장치의 안전거리&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전거리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$D = 1 {,} 600 ( T_{c} + T_{s} )$ [mm]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;$T_{c}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;빛을 가린 뒤 급정지장치가 작동을 시작할 때까지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.05초&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;$T_{s}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;급정지장치가 작동해 슬라이드가 멈출 때까지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.15초&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1,600&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사람 손이 뻗는 속도 [mm/s]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH47" s="32" t="inlineStr">
         <is>
-          <t>① 80 [mm] 는 계산과 맞지 않는다.&lt;br&gt;② 160 [mm] 는 0.1초로 잡은 값이다.&lt;br&gt;③ 240 [mm] 는 0.15초로 잡은 값이다.</t>
+          <t>① 80 [mm]는 계산과 맞지 않는다.&lt;br&gt;② 160 [mm]는 0.1초로 잡은 값이다.&lt;br&gt;③ 240 [mm]는 0.15초로 잡은 값이다.</t>
         </is>
       </c>
       <c r="AI47" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;광전자식 방호장치의 안전거리&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;두 시간을 반드시 더해야&lt;/strong&gt; 한다 — &lt;strong&gt;하나만 넣으면 160 이나 240 이 나와 보기에 그대로 놓여&lt;/strong&gt; 있다. &lt;strong&gt;「총 소요시간」&lt;/strong&gt;이라는 점을 놓치지 않는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $D = 1 {,} 600 ( T_{c} + T_{s} )$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;광전자식 방호장치의 안전거리&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;두 시간을 반드시 더해야&lt;/strong&gt; 한다 — &lt;strong&gt;하나만 넣으면 160 이나 240이 나와 보기에 그대로 놓여&lt;/strong&gt; 있다. &lt;strong&gt;「총 소요시간」&lt;/strong&gt;이라는 점을 놓치지 않는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $D = 1 {,} 600 ( T_{c} + T_{s} )$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7482,17 +7482,17 @@
       </c>
       <c r="AG50" s="32" t="inlineStr">
         <is>
-          <t>단면적은 $A = \pi \times 15^{2} = 706.9$ [mm²] 이므로 응력은 $\dfrac{31 {,} 400}{706.9} = 44.4$ [MPa] 다. $S = \dfrac{380}{44.4} \fallingdotseq 8.55$ 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전율의 셈&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;셈&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;① 단면적&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$A = \dfrac{\pi d^{2}}{4} = \pi \times 15^{2} = 706.9$ [mm²]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;② 작용응력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;31,400 [N] ÷ 706.9 [mm²] = 44.4 [MPa]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 [MPa] = 1 [N/mm²]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;③ 안전율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$S = \dfrac{380}{44.4} = 8.55$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>단면적은 $A = \pi \times 15^{2} = 706.9$ [mm²]이므로 응력은 $\dfrac{31 {,} 400}{706.9} = 44.4$ [MPa]다. $S = \dfrac{380}{44.4} \fallingdotseq 8.55$다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전율의 셈&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;셈&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;① 단면적&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$A = \dfrac{\pi d^{2}}{4} = \pi \times 15^{2} = 706.9$ [mm²]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;② 작용응력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;31,400 [N] ÷ 706.9 [mm²] = 44.4 [MPa]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 [MPa] = 1 [N/mm²]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;③ 안전율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$S = \dfrac{380}{44.4} = 8.55$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH50" s="32" t="inlineStr">
         <is>
-          <t>① 9.62 는 계산과 맞지 않는다.&lt;br&gt;③ 7.86 도 그렇다.&lt;br&gt;④ 6.54 도 그렇다.</t>
+          <t>① 9.62는 계산과 맞지 않는다.&lt;br&gt;③ 7.86 도 그렇다.&lt;br&gt;④ 6.54 도 그렇다.</t>
         </is>
       </c>
       <c r="AI50" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전율(안전계수)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;[kN] 을 [N] 으로, 지름을 반지름으로 고치는 두 곳&lt;/strong&gt;에서 대부분 어긋난다. &lt;strong&gt;N 과 mm 로 통일하면 응력이 곧바로 [MPa]&lt;/strong&gt;로 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;안전율 = 인장강도 ÷ 작용응력&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;안전율(안전계수)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;[kN]을 [N]으로, 지름을 반지름으로 고치는 두 곳&lt;/strong&gt;에서 대부분 어긋난다. &lt;strong&gt;N과 mm로 통일하면 응력이 곧바로 [MPa]&lt;/strong&gt;로 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;안전율 = 인장강도 ÷ 작용응력&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7879,7 +7879,7 @@
       </c>
       <c r="AI53" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;목재가공용 둥근톱의 분할날&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;분할날이 톱날에서 멀면 켠 자리가 그 사이에서 오므라들어&lt;/strong&gt; 소용이 없다 — &lt;strong&gt;12 [mm] 는 그 틈의 한계&lt;/strong&gt;다. &lt;strong&gt;덮개 하단 8 [mm] 와 갈라&lt;/strong&gt; 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;톱날 원주면과 12 [mm] 이내&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;목재가공용 둥근톱의 분할날&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;분할날이 톱날에서 멀면 켠 자리가 그 사이에서 오므라들어&lt;/strong&gt; 소용이 없다 — &lt;strong&gt;12 [mm]는 그 틈의 한계&lt;/strong&gt;다. &lt;strong&gt;덮개 하단 8 [mm]와 갈라&lt;/strong&gt; 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;톱날 원주면과 12 [mm] 이내&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8003,12 +8003,12 @@
       </c>
       <c r="AH54" s="32" t="inlineStr">
         <is>
-          <t>② 400 [mm] 는 기준값이 아니다.&lt;br&gt;③ 200 [mm] 는 기준에 못 미친다.&lt;br&gt;④ 100 [mm] 도 그렇다.</t>
+          <t>② 400 [mm]는 기준값이 아니다.&lt;br&gt;③ 200 [mm]는 기준에 못 미친다.&lt;br&gt;④ 100 [mm] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI54" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;양수조작식 방호장치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;300 [mm] 는 두 손을 벌려야 닿는 거리&lt;/strong&gt;다 — &lt;strong&gt;그보다 가까우면 한 손과 팔꿈치로 눌러 버릴 수&lt;/strong&gt; 있어 방호가 무너진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;누름버튼 사이 300 [mm] 이상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;양수조작식 방호장치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;300 [mm]는 두 손을 벌려야 닿는 거리&lt;/strong&gt;다 — &lt;strong&gt;그보다 가까우면 한 손과 팔꿈치로 눌러 버릴 수&lt;/strong&gt; 있어 방호가 무너진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;누름버튼 사이 300 [mm] 이상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="AH56" s="32" t="inlineStr">
         <is>
-          <t>① 60% 는 기준값이 아니다.&lt;br&gt;② 65% 도 그렇다.&lt;br&gt;④ 75% 도 그렇다.</t>
+          <t>① 60%는 기준값이 아니다.&lt;br&gt;② 65% 도 그렇다.&lt;br&gt;④ 75% 도 그렇다.</t>
         </is>
       </c>
       <c r="AI56" s="32" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="AG58" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;회전축 중량 1톤 초과, 원주속도 초당 120 [m] 이상&lt;/strong&gt;인 고속회전체다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;고속회전체의 안전기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비파괴검사 대상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;회전축 중량 1톤 초과 + 원주속도 초당 120 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;회전시험 중의 위험 방지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전용 시험실에서 하거나 견고한 격벽을 설치&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고속회전체의 정의&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;원주속도가 초당 25 [m] 를 넘는 회전체&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;회전축 중량 1톤 초과, 원주속도 초당 120 [m] 이상&lt;/strong&gt;인 고속회전체다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;고속회전체의 안전기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비파괴검사 대상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;회전축 중량 1톤 초과 + 원주속도 초당 120 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;회전시험 중의 위험 방지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전용 시험실에서 하거나 견고한 격벽을 설치&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고속회전체의 정의&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;원주속도가 초당 25 [m]를 넘는 회전체&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH58" s="32" t="inlineStr">
@@ -9040,7 +9040,7 @@
       </c>
       <c r="AI62" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;프레스 페달의 방호&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;나머지 셋은 모두 「풀리거나 움직이지 않게 죄는」 부품&lt;/strong&gt;이라 발을 막을 수 없다. &lt;strong&gt;덮는 것은 커버 하나&lt;/strong&gt; 뿐이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;페달에는 U자형 커버&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;프레스 페달의 방호&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;나머지 셋은 모두 「풀리거나 움직이지 않게 죄는」 부품&lt;/strong&gt;이라 발을 막을 수 없다. &lt;strong&gt;덮는 것은 커버 하나&lt;/strong&gt;뿐이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;페달에는 U자형 커버&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9417,7 +9417,7 @@
       </c>
       <c r="AG65" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;30 [mA], 0.03초&lt;/strong&gt;다. &lt;strong&gt;감전을 막으려면 심실세동에 이르기 전에 끊어야&lt;/strong&gt; 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;감전방지용 누전차단기&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정격감도전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;30 [mA] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;동작시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.03초 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;물기가 있는 장소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;15 [mA] 이하, 0.03초 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;까닭&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;심실세동전류 &lt;/u&gt;$I = 165 / \sqrt{T}$&lt;u&gt; [mA]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;T 가 짧을수록 견딜 수 있는 전류가 크다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;30 [mA], 0.03초&lt;/strong&gt;다. &lt;strong&gt;감전을 막으려면 심실세동에 이르기 전에 끊어야&lt;/strong&gt; 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;감전방지용 누전차단기&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정격감도전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;30 [mA] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;동작시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.03초 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;물기가 있는 장소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;15 [mA] 이하, 0.03초 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;까닭&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;심실세동전류 &lt;/u&gt;$I = 165 / \sqrt{T}$&lt;u&gt; [mA]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;T가 짧을수록 견딜 수 있는 전류가 크다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH65" s="32" t="inlineStr">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="AI65" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;누전차단기의 동작시간&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;보기 넷이 감도전류는 모두 같고 시간만 다르다&lt;/strong&gt; — &lt;strong&gt;가장 빠른 0.03초&lt;/strong&gt;가 답이다. &lt;strong&gt;심실세동전류가 &lt;/strong&gt;$165 / \sqrt{T}$&lt;strong&gt; 이므로 시간이 짧을수록 사람이 견딘다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;감전방지용은 30 [mA], 0.03초&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;누전차단기의 동작시간&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;보기 넷이 감도전류는 모두 같고 시간만 다르다&lt;/strong&gt; — &lt;strong&gt;가장 빠른 0.03초&lt;/strong&gt;가 답이다. &lt;strong&gt;심실세동전류가 &lt;/strong&gt;$165 / \sqrt{T}$&lt;strong&gt;이므로 시간이 짧을수록 사람이 견딘다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;감전방지용은 30 [mA], 0.03초&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="AG67" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;건조한 곳&lt;/strong&gt;은 감전될 여지가 적어 면제된다. &lt;strong&gt;나머지 셋은 물기·발열·임시배선&lt;/strong&gt;이라 설치해야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;누전차단기의 설치와 면제&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td rowspan="5" style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;설치해야 하는 곳&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;대지전압 150 [V] 를 넘는 이동형·휴대형 기계기구&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;물 등 도전성 액체가 있는 습윤장소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;대지전압에 관계없이&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;철판·철골 위 등 도전성이 높은 장소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;임시배선의 전원&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;콘크리트 직접 매설 케이블 포함&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;파이프라인 등 발열장치에 공급하는 전로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;면제되는 곳&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;건조한 곳에 시설하고 건조한 곳에서 조작하는 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;건조한 곳&lt;/strong&gt;은 감전될 여지가 적어 면제된다. &lt;strong&gt;나머지 셋은 물기·발열·임시배선&lt;/strong&gt;이라 설치해야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;누전차단기의 설치와 면제&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td rowspan="5" style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;설치해야 하는 곳&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;대지전압 150 [V]를 넘는 이동형·휴대형 기계기구&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;물 등 도전성 액체가 있는 습윤장소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;대지전압에 관계없이&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;철판·철골 위 등 도전성이 높은 장소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;임시배선의 전원&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;콘크리트 직접 매설 케이블 포함&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;파이프라인 등 발열장치에 공급하는 전로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;면제되는 곳&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;건조한 곳에 시설하고 건조한 곳에서 조작하는 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH67" s="32" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AI68" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;가수전류와 불수전류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「가(可) 수(手)」는 「손을 뗄 수 있다」&lt;/strong&gt;는 뜻이고 &lt;strong&gt;「불수(不手)」는 그 반대&lt;/strong&gt;다. &lt;strong&gt;감전방지용 누전차단기를 30 [mA] 로 잡는 것도 이 한계 언저리&lt;/strong&gt; 이기 때문이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;가수전류는 스스로 뗄 수 있는 전류&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;가수전류와 불수전류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「가(可) 수(手)」는 「손을 뗄 수 있다」&lt;/strong&gt;는 뜻이고 &lt;strong&gt;「불수(不手)」는 그 반대&lt;/strong&gt;다. &lt;strong&gt;감전방지용 누전차단기를 30 [mA]로 잡는 것도 이 한계 언저리&lt;/strong&gt; 이기 때문이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;가수전류는 스스로 뗄 수 있는 전류&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9935,7 +9935,7 @@
       </c>
       <c r="AI69" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;지중전선로의 매설깊이&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「1.0 과 0.6」&lt;/strong&gt; 두 값이다 — &lt;strong&gt;차가 지나면 1 [m], 아니면 0.6 [m]&lt;/strong&gt;. &lt;strong&gt;KEC 로 바뀌면서 옛 1.2 [m] 가 1.0 [m] 로 낮아졌다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;압력을 받지 않으면 0.6 [m] 이상&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; &lt;u&gt;KEC 시행(2021.1.1)&lt;/u&gt;으로 중량물의 압력을 받는 장소의 매설깊이가 &lt;u&gt;1.2 [m] 에서 1.0 [m] 로&lt;/u&gt; 바뀌었다. 옛 수치(1.2 / 0.6)로 외워 두지 말 것.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;지중전선로의 매설깊이&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「1.0과 0.6」&lt;/strong&gt; 두 값이다 — &lt;strong&gt;차가 지나면 1 [m], 아니면 0.6 [m]&lt;/strong&gt;. &lt;strong&gt;KEC로 바뀌면서 옛 1.2 [m]가 1.0 [m]로 낮아졌다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;압력을 받지 않으면 0.6 [m] 이상&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; &lt;u&gt;KEC 시행(2021.1.1)&lt;/u&gt;으로 중량물의 압력을 받는 장소의 매설깊이가 &lt;u&gt;1.2 [m]에서 1.0 [m]로&lt;/u&gt; 바뀌었다. 옛 수치(1.2 / 0.6)로 외워 두지 말 것.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10054,17 +10054,17 @@
       </c>
       <c r="AG70" s="32" t="inlineStr">
         <is>
-          <t>누설전류는 &lt;strong&gt;최대공급전류의 1/2,000 이하&lt;/strong&gt; 라야 하므로 $\dfrac{200}{2 {,} 000} = 0.1$ [A] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;누설전류의 한도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기준&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;누설전류는 최대공급전류의 1/2,000 을 넘지 않을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;200 ÷ 2,000 = 0.1 [A]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;= 100 [mA]&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;절연저항으로 보면&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$R = \dfrac{V}{I_{g}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;누설전류가 작을수록 절연저항이 크다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>누설전류는 &lt;strong&gt;최대공급전류의 1/2,000 이하&lt;/strong&gt;라야 하므로 $\dfrac{200}{2 {,} 000} = 0.1$ [A]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;누설전류의 한도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기준&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;누설전류는 최대공급전류의 1/2,000을 넘지 않을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;200 ÷ 2,000 = 0.1 [A]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;= 100 [mA]&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;절연저항으로 보면&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$R = \dfrac{V}{I_{g}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;누설전류가 작을수록 절연저항이 크다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH70" s="32" t="inlineStr">
         <is>
-          <t>② 0.2 [A] 는 1/1,000 로 잡은 값이다.&lt;br&gt;③ 1 [A] 는 자릿수가 어긋난다.&lt;br&gt;④ 2 [A] 도 그렇다.</t>
+          <t>② 0.2 [A]는 1/1,000로 잡은 값이다.&lt;br&gt;③ 1 [A]는 자릿수가 어긋난다.&lt;br&gt;④ 2 [A] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI70" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;누설전류의 한도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「2,000분의 1」&lt;/strong&gt;이라는 분수 하나면 풀린다 — &lt;strong&gt;200 [A] 의 2,000분의 1 은 0.1 [A]&lt;/strong&gt;. &lt;strong&gt;감전방지용 누전차단기의 30 [mA] 와는 다른 기준&lt;/strong&gt;이라는 점도 갈라 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;누설전류는 최대공급전류의 1/2,000 이하&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;누설전류의 한도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「2,000분의 1」&lt;/strong&gt;이라는 분수 하나면 풀린다 — &lt;strong&gt;200 [A]의 2,000분의 1은 0.1 [A]&lt;/strong&gt;. &lt;strong&gt;감전방지용 누전차단기의 30 [mA] 와는 다른 기준&lt;/strong&gt;이라는 점도 갈라 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;누설전류는 최대공급전류의 1/2,000 이하&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10536,7 +10536,7 @@
       </c>
       <c r="U74" s="32" t="inlineStr">
         <is>
-          <t>두 물체의 마찰로 3000V의 정전기가 생겼다. 폭발성 위험의 장소에서 두 물체의 정전용량은 약 몇 pF 이면 폭발로 이어지겠는가? (단, 착화에너지는 0.25mJ 이다.)</t>
+          <t>두 물체의 마찰로 3000V의 정전기가 생겼다. 폭발성 위험의 장소에서 두 물체의 정전용량은 약 몇 pF 이면 폭발로 이어지겠는가? (단, 착화에너지는 0.25mJ이다.)</t>
         </is>
       </c>
       <c r="V74" s="32" t="inlineStr"/>
@@ -10570,17 +10570,17 @@
       </c>
       <c r="AG74" s="32" t="inlineStr">
         <is>
-          <t>$W = \dfrac{1}{2} C V^{2}$ 이므로 $C = \dfrac{2 W}{V^{2}} = \dfrac{2 \times 0.25 \times 10^{-3}}{3 {,} 000^{2}} = 5.6 \times 10^{-11}$ [F] = 56 [pF] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;정전기 에너지&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;방전에너지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$W = \dfrac{1}{2} C V^{2}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;[J]&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정전용량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$C = \dfrac{2 W}{V^{2}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전위&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$V = \sqrt{\dfrac{2 W}{C}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;단위&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 [pF] = 10⁻¹² [F], 1 [mJ] = 10⁻³ [J]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$W = \dfrac{1}{2} C V^{2}$이므로 $C = \dfrac{2 W}{V^{2}} = \dfrac{2 \times 0.25 \times 10^{-3}}{3 {,} 000^{2}} = 5.6 \times 10^{-11}$ [F] = 56 [pF]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;정전기 에너지&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;방전에너지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$W = \dfrac{1}{2} C V^{2}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;[J]&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정전용량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$C = \dfrac{2 W}{V^{2}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전위&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$V = \sqrt{\dfrac{2 W}{C}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;단위&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 [pF] = 10⁻¹² [F], 1 [mJ] = 10⁻³ [J]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH74" s="32" t="inlineStr">
         <is>
-          <t>① 14 [pF] 는 계산과 맞지 않는다.&lt;br&gt;② 28 [pF] 는 절반으로 잡은 값이다.&lt;br&gt;③ 45 [pF] 도 맞지 않는다.</t>
+          <t>① 14 [pF]는 계산과 맞지 않는다.&lt;br&gt;② 28 [pF]는 절반으로 잡은 값이다.&lt;br&gt;③ 45 [pF] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI74" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;정전기 방전에너지&lt;/strong&gt;&lt;br&gt;$C = 2 W / V^{2}$ 에서 &lt;strong&gt;분모가 3,000의 제곱 = 9 × 10⁶&lt;/strong&gt;이다 — &lt;strong&gt;분자 5 × 10⁻⁴ 를 나누면 5.6 × 10⁻¹¹ [F]&lt;/strong&gt;. &lt;strong&gt;[F] 를 [pF] 로 바꿀 때 10¹² 를 곱한다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $C = 2 W / V^{2}$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;정전기 방전에너지&lt;/strong&gt;&lt;br&gt;$C = 2 W / V^{2}$에서 &lt;strong&gt;분모가 3,000의 제곱 = 9 × 10⁶&lt;/strong&gt;이다 — &lt;strong&gt;분자 5 × 10⁻⁴ 를 나누면 5.6 × 10⁻¹¹ [F]&lt;/strong&gt;. &lt;strong&gt;[F]를 [pF]로 바꿀 때 10¹² 를 곱한다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $C = 2 W / V^{2}$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10967,7 +10967,7 @@
       </c>
       <c r="AI77" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;주택용 배선차단기&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;B → C → D 로 갈수록 돌입전류를 너그럽게&lt;/strong&gt; 받아 준다 — &lt;strong&gt;「3~5 · 5~10 · 10~20」&lt;/strong&gt;으로 배수가 커진다. &lt;strong&gt;돌입전류가 큰 부하일수록 뒤쪽 타입&lt;/strong&gt;을 쓴다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;B 는 3In ~ 5In&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;주택용 배선차단기&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;B → C → D로 갈수록 돌입전류를 너그럽게&lt;/strong&gt; 받아 준다 — &lt;strong&gt;「3~5 · 5~10 · 10~20」&lt;/strong&gt;으로 배수가 커진다. &lt;strong&gt;돌입전류가 큰 부하일수록 뒤쪽 타입&lt;/strong&gt;을 쓴다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;B는 3In ~ 5In&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11086,17 +11086,17 @@
       </c>
       <c r="AG78" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;파두시간 × 파미에서 파고치의 50% 로 줄 때까지의 시간&lt;/strong&gt;으로 나타낸다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;충격파(서지)의 표시&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;표시법&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;파두시간 × 파미에서 파고치의 50% 로 감소할 때까지의 시간&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;표준 충격파형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.2 × 50 [μs]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;파두시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0 에서 파고치에 이르기까지&lt;/u&gt; — 1.2 [μs]&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;파미시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;파고치의 50% 로 줄기까지&lt;/u&gt; — 50 [μs]&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;파두시간 × 파미에서 파고치의 50%로 줄 때까지의 시간&lt;/strong&gt;으로 나타낸다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;충격파(서지)의 표시&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;표시법&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;파두시간 × 파미에서 파고치의 50%로 감소할 때까지의 시간&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;표준 충격파형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.2 × 50 [μs]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;파두시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0에서 파고치에 이르기까지&lt;/u&gt; — 1.2 [μs]&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;파미시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;파고치의 50%로 줄기까지&lt;/u&gt; — 50 [μs]&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH78" s="32" t="inlineStr">
         <is>
-          <t>① 63% 가 아니라 50% 다.&lt;br&gt;③ 「파장시간」이 아니라 「파두시간」이다.&lt;br&gt;④ 파장시간과 63% 도 모두 맞지 않는다.</t>
+          <t>① 63%가 아니라 50%다.&lt;br&gt;③ 「파장시간」이 아니라 「파두시간」이다.&lt;br&gt;④ 파장시간과 63% 도 모두 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI78" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;충격파의 표시&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;표준 충격파형 「1.2 × 50 [μs]」&lt;/strong&gt;를 떠올리면 앞은 파두, 뒤는 반값(50%)까지의 시간임을 곧 알 수 있다. &lt;strong&gt;63% 는 시정수의 값&lt;/strong&gt;이라 다른 자리의 숫자다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;파두시간 × 반값까지의 시간&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;충격파의 표시&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;표준 충격파형 「1.2 × 50 [μs]」&lt;/strong&gt;를 떠올리면 앞은 파두, 뒤는 반값(50%)까지의 시간임을 곧 알 수 있다. &lt;strong&gt;63%는 시정수의 값&lt;/strong&gt;이라 다른 자리의 숫자다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;파두시간 × 반값까지의 시간&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11220,7 +11220,7 @@
       </c>
       <c r="AH79" s="32" t="inlineStr">
         <is>
-          <t>② 제2종은 150 [Ω] 이 아니라 「150 ÷ 1선 지락전류」 [Ω] 이하다.&lt;br&gt;③ 제3종은 10 [Ω] 이 아니라 100 [Ω] 이하다.&lt;br&gt;④ 특별 제3종은 100 [Ω] 이 아니라 10 [Ω] 이하다.</t>
+          <t>② 제2종은 150 [Ω]이 아니라 「150 ÷ 1선 지락전류」 [Ω] 이하다.&lt;br&gt;③ 제3종은 10 [Ω]이 아니라 100 [Ω] 이하다.&lt;br&gt;④ 특별 제3종은 100 [Ω]이 아니라 10 [Ω] 이하다.</t>
         </is>
       </c>
       <c r="AI79" s="32" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="AI80" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;접지공사의 적용 대상&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「고압」이라는 말이 붙으면 제1종&lt;/strong&gt;이다 — &lt;strong&gt;다만 「고압계기용 변압기의 2차측」은 저압이라 제3종&lt;/strong&gt;이라는 점이 갈림길이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;고압용 케이블트레이는 제1종&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; &lt;u&gt;KEC 시행(2021.1.1)&lt;/u&gt;으로 &lt;u&gt;접지공사의 종별 구분이 폐지&lt;/u&gt; 하였다. 이 문항은 옛 기준에 따른 것이므로 조문을 찾을 때에는 현행 KEC 의 보호접지 규정을 볼 것.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;접지공사의 적용 대상&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「고압」이라는 말이 붙으면 제1종&lt;/strong&gt;이다 — &lt;strong&gt;다만 「고압계기용 변압기의 2차측」은 저압이라 제3종&lt;/strong&gt;이라는 점이 갈림길이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;고압용 케이블트레이는 제1종&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; &lt;u&gt;KEC 시행(2021.1.1)&lt;/u&gt;으로 &lt;u&gt;접지공사의 종별 구분이 폐지&lt;/u&gt; 하였다. 이 문항은 옛 기준에 따른 것이므로 조문을 찾을 때에는 현행 KEC의 보호접지 규정을 볼 것.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11478,12 +11478,12 @@
       </c>
       <c r="AH81" s="32" t="inlineStr">
         <is>
-          <t>① 침대침 전극은 훨씬 낮은 전압에서 방전한다.&lt;br&gt;③ 1 [mm] 평행판은 약 3 [kV] 에서 방전한다.&lt;br&gt;④ 1 [mm] 침대침 전극은 더욱 낮다.</t>
+          <t>① 침대침 전극은 훨씬 낮은 전압에서 방전한다.&lt;br&gt;③ 1 [mm] 평행판은 약 3 [kV]에서 방전한다.&lt;br&gt;④ 1 [mm] 침대침 전극은 더욱 낮다.</t>
         </is>
       </c>
       <c r="AI81" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;공기의 절연파괴&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;30 [kV/cm]&lt;/strong&gt;라는 값 하나면 풀린다 — &lt;strong&gt;1 [cm] × 30 [kV/cm] = 30 [kV]&lt;/strong&gt;. &lt;strong&gt;뾰족한 전극은 전계가 한 점에 몰려 같은 거리라도 훨씬 낮은 전압에서&lt;/strong&gt; 터진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;공기는 30 [kV/cm] 에서 파괴&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;공기의 절연파괴&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;30 [kV/cm]&lt;/strong&gt;라는 값 하나면 풀린다 — &lt;strong&gt;1 [cm] × 30 [kV/cm] = 30 [kV]&lt;/strong&gt;. &lt;strong&gt;뾰족한 전극은 전계가 한 점에 몰려 같은 거리라도 훨씬 낮은 전압에서&lt;/strong&gt; 터진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;공기는 30 [kV/cm]에서 파괴&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11612,7 +11612,7 @@
       </c>
       <c r="AI82" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;정전기와 동전기의 재해&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;정전기는 에너지가 작아 사람을 죽이지는 못하지만 「깜짝 놀라게」&lt;/strong&gt; 한다 — &lt;strong&gt;사다리 위에서 놀라 떨어지는 것이 정전기 재해의 흔한 꼴&lt;/strong&gt;이다. &lt;strong&gt;그 점만 동전기와 겹친다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;놀라 떨어지는 것은 둘의 공통&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;정전기와 동전기의 재해&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;정전기는 에너지가 작아 사람을 죽이지는 못하지만 「깜짝 놀라게」&lt;/strong&gt;한다 — &lt;strong&gt;사다리 위에서 놀라 떨어지는 것이 정전기 재해의 흔한 꼴&lt;/strong&gt;이다. &lt;strong&gt;그 점만 동전기와 겹친다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;놀라 떨어지는 것은 둘의 공통&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12115,7 +12115,7 @@
       </c>
       <c r="AH86" s="32" t="inlineStr">
         <is>
-          <t>② 폭굉 시 발생압력이 초기압력의 20 ~ 50배인 것은 맞다.&lt;br&gt;③ 분해반응의 화염온도가 3,100 [℃] 인 것도 맞다.&lt;br&gt;④ 용단·가열작업 시 1.3 [kgf/cm²] 를 넘겨서는 안 되는 것도 맞다.</t>
+          <t>② 폭굉 시 발생압력이 초기압력의 20 ~ 50배인 것은 맞다.&lt;br&gt;③ 분해반응의 화염온도가 3,100 [℃] 인 것도 맞다.&lt;br&gt;④ 용단·가열작업 시 1.3 [kgf/cm²]를 넘겨서는 안 되는 것도 맞다.</t>
         </is>
       </c>
       <c r="AI86" s="32" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="AH88" s="32" t="inlineStr">
         <is>
-          <t>① 20% 는 염산·황산·질산의 기준이다.&lt;br&gt;③ 50% 는 기준에 없는 값이다.&lt;br&gt;④ 60% 는 인산·아세트산·불산의 기준이다.</t>
+          <t>① 20%는 염산·황산·질산의 기준이다.&lt;br&gt;③ 50%는 기준에 없는 값이다.&lt;br&gt;④ 60%는 인산·아세트산·불산의 기준이다.</t>
         </is>
       </c>
       <c r="AI88" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;부식성 물질&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;숫자가 「20 · 60 · 40」&lt;/strong&gt; 셋뿐이다 — &lt;strong&gt;센 산 20, 약한 산 60, 염기 40&lt;/strong&gt;. &lt;strong&gt;보기에 20 과 60 이 함께 놓여 산의 기준으로 끌어당긴다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;염기류는 40% 이상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;부식성 물질&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;숫자가 「20 · 60 · 40」&lt;/strong&gt; 셋뿐이다 — &lt;strong&gt;센 산 20, 약한 산 60, 염기 40&lt;/strong&gt;. &lt;strong&gt;보기에 20과 60이 함께 놓여 산의 기준으로 끌어당긴다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;염기류는 40% 이상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12636,7 +12636,7 @@
       </c>
       <c r="AI90" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;아세틸렌의 분해폭발&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;아세틸렌은 「공기가 없어도 터진다」&lt;/strong&gt; — &lt;strong&gt;그래서 용기에 그냥 담지 못하고 아세톤에 녹여 다공물질에 스며들게&lt;/strong&gt; 해 둔다. &lt;strong&gt;사용압력을 127 [kPa] 로 묶는 까닭&lt;/strong&gt;도 여기 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;아세틸렌은 분해폭발한다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;아세틸렌의 분해폭발&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;아세틸렌은 「공기가 없어도 터진다」&lt;/strong&gt; — &lt;strong&gt;그래서 용기에 그냥 담지 못하고 아세톤에 녹여 다공물질에 스며들게&lt;/strong&gt; 해 둔다. &lt;strong&gt;사용압력을 127 [kPa]로 묶는 까닭&lt;/strong&gt;도 여기 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;아세틸렌은 분해폭발한다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12979,7 +12979,7 @@
       </c>
       <c r="U93" s="32" t="inlineStr">
         <is>
-          <t>송풍기의 회전차 속도가 1300rpm 일 때 송풍량이 분당 300m3 이었다. 송풍량을 분당 400m3 으로 증가시키고자 한다면 송풍기의 회전차 속도는 약 몇 rpm으로 하여야 하는가?</t>
+          <t>송풍기의 회전차 속도가 1300rpm 일 때 송풍량이 분당 300m3 이었다. 송풍량을 분당 400m3으로 증가시키고자 한다면 송풍기의 회전차 속도는 약 몇 rpm으로 하여야 하는가?</t>
         </is>
       </c>
       <c r="V93" s="32" t="inlineStr"/>
@@ -13013,17 +13013,17 @@
       </c>
       <c r="AG93" s="32" t="inlineStr">
         <is>
-          <t>풍량은 &lt;strong&gt;회전수에 그대로 비례&lt;/strong&gt; 한다.$N_{2} = N_{1} \times \dfrac{Q_{2}}{Q_{1}} = 1 {,} 300 \times \dfrac{400}{300} \fallingdotseq 1 {,} 733 \, \mathrm{rpm}$&lt;div style="margin:12px 0 2px;font-weight:700"&gt;송풍기의 상사법칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;관계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;풍량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$Q \propto N$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1승&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;풍압&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$P \propto N^{2}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;제곱&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;소요동력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$L \propto N^{3}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;세제곱&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;계산&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1,300 × 400/300 ≒ 1,733&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>풍량은 &lt;strong&gt;회전수에 그대로 비례&lt;/strong&gt;한다.$N_{2} = N_{1} \times \dfrac{Q_{2}}{Q_{1}} = 1 {,} 300 \times \dfrac{400}{300} \fallingdotseq 1 {,} 733 \, \mathrm{rpm}$&lt;div style="margin:12px 0 2px;font-weight:700"&gt;송풍기의 상사법칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;관계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;풍량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$Q \propto N$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1승&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;풍압&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$P \propto N^{2}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;제곱&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;소요동력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$L \propto N^{3}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;세제곱&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;계산&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1,300 × 400/300 ≒ 1,733&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH93" s="32" t="inlineStr">
         <is>
-          <t>① 1533rpm 은 계산과 맞지 않는다.&lt;br&gt;③ 1967rpm 도 그렇다.&lt;br&gt;④ 2167rpm 은 제곱 관계로 잘못 잡은 값이다.</t>
+          <t>① 1533rpm은 계산과 맞지 않는다.&lt;br&gt;③ 1967rpm 도 그렇다.&lt;br&gt;④ 2167rpm은 제곱 관계로 잘못 잡은 값이다.</t>
         </is>
       </c>
       <c r="AI93" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;송풍기의 상사법칙&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;풍량만은 회전수에 그대로 비례&lt;/strong&gt; 한다 — &lt;strong&gt;300 → 400 이니 4/3 배, 1,300 × 4/3 ≒ 1,733&lt;/strong&gt;이다. &lt;strong&gt;제곱이나 세제곱을 쓰면 값이 훌쩍 커진다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;풍량은 회전수에 비례&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;송풍기의 상사법칙&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;풍량만은 회전수에 그대로 비례&lt;/strong&gt;한다 — &lt;strong&gt;300 → 400 이니 4/3 배, 1,300 × 4/3 ≒ 1,733&lt;/strong&gt;이다. &lt;strong&gt;제곱이나 세제곱을 쓰면 값이 훌쩍 커진다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;풍량은 회전수에 비례&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13142,17 +13142,17 @@
       </c>
       <c r="AG94" s="32" t="inlineStr">
         <is>
-          <t>에어로졸은 &lt;strong&gt;mg/m³&lt;/strong&gt;로 나타낸다. &lt;strong&gt;부피비인 ppm 을 쓸 수 없다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;노출기준의 표시단위&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;유해인자&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단위&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가스 · 증기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;ppm 또는 mg/m³&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;부피비를 쓸 수 있다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;에어로졸(분진 · 흄 · 미스트)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;mg/m³&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;ppm 이 아니다&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;석면 · 내화성 세라믹섬유&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개/cm³&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;섬유의 개수&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고온&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;습구흑구온도지수(WBGT) [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>에어로졸은 &lt;strong&gt;mg/m³&lt;/strong&gt;로 나타낸다. &lt;strong&gt;부피비인 ppm을 쓸 수 없다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;노출기준의 표시단위&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;유해인자&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단위&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가스 · 증기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;ppm 또는 mg/m³&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;부피비를 쓸 수 있다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;에어로졸(분진 · 흄 · 미스트)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;mg/m³&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;ppm이 아니다&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;석면 · 내화성 세라믹섬유&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개/cm³&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;섬유의 개수&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고온&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;습구흑구온도지수(WBGT) [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH94" s="32" t="inlineStr">
         <is>
-          <t>② 증기는 ppm 으로 나타낸다.&lt;br&gt;③ 가스도 그렇다.&lt;br&gt;④ 고온은 습구흑구온도지수로 나타낸다.</t>
+          <t>② 증기는 ppm으로 나타낸다.&lt;br&gt;③ 가스도 그렇다.&lt;br&gt;④ 고온은 습구흑구온도지수로 나타낸다.</t>
         </is>
       </c>
       <c r="AI94" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;노출기준의 표시단위&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;ppm 은 「기체 부피의 백만분율」&lt;/strong&gt;이라 &lt;strong&gt;기체(가스 · 증기)에만 쓸 수&lt;/strong&gt; 있다. &lt;strong&gt;에어로졸은 알갱이라 무게(mg/m³), 섬유는 개수(개/cm³)&lt;/strong&gt;로 센다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;에어로졸은 mg/m³&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;노출기준의 표시단위&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;ppm은 「기체 부피의 백만분율」&lt;/strong&gt;이라 &lt;strong&gt;기체(가스 · 증기)에만 쓸 수&lt;/strong&gt; 있다. &lt;strong&gt;에어로졸은 알갱이라 무게(mg/m³), 섬유는 개수(개/cm³)&lt;/strong&gt;로 센다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;에어로졸은 mg/m³&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13529,17 +13529,17 @@
       </c>
       <c r="AG97" s="32" t="inlineStr">
         <is>
-          <t>$\text{플래시율} = \dfrac{1.45 - 1}{540} = \dfrac{0.45}{540} \fallingdotseq 0.00083$ 이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;플래시율(flash율)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;플래시율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{엔탈피 차}}{\text{기화열}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;엔탈피 차&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.45 − 1 = 0.45 [kcal/kg]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기화열&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;540 [cal/g] = 540 [kcal/kg]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;단위가 같아진다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;결과&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.45 ÷ 540 = 0.00083&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;뜻&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;압력이 풀릴 때 곧바로 증발하는 액체의 비율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$\text{플래시율} = \dfrac{1.45 - 1}{540} = \dfrac{0.45}{540} \fallingdotseq 0.00083$이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;플래시율(flash율)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;플래시율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{엔탈피 차}}{\text{기화열}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;엔탈피 차&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.45 − 1 = 0.45 [kcal/kg]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기화열&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;540 [cal/g] = 540 [kcal/kg]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;단위가 같아진다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;결과&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.45 ÷ 540 = 0.00083&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;뜻&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;압력이 풀릴 때 곧바로 증발하는 액체의 비율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH97" s="32" t="inlineStr">
         <is>
-          <t>② 0.0083 은 자릿수가 한 자리 어긋난다.&lt;br&gt;③ 0.0015 는 계산과 맞지 않는다.&lt;br&gt;④ 0.015 도 그렇다.</t>
+          <t>② 0.0083은 자릿수가 한 자리 어긋난다.&lt;br&gt;③ 0.0015는 계산과 맞지 않는다.&lt;br&gt;④ 0.015 도 그렇다.</t>
         </is>
       </c>
       <c r="AI97" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;플래시율&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;[cal/g] 과 [kcal/kg] 이 같은 값&lt;/strong&gt;이라는 것이 이 셈의 열쇠다 — &lt;strong&gt;둘 다 1,000배씩이라 그대로 나눌 수&lt;/strong&gt; 있다. &lt;strong&gt;0.45/540 은 대략 1/1,200 이므로 0.0008&lt;/strong&gt; 언저리다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;플래시율 = 엔탈피 차 ÷ 기화열&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;플래시율&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;[cal/g]과 [kcal/kg]이 같은 값&lt;/strong&gt;이라는 것이 이 셈의 열쇠다 — &lt;strong&gt;둘 다 1,000배씩이라 그대로 나눌 수&lt;/strong&gt; 있다. &lt;strong&gt;0.45/540은 대략 1/1,200이므로 0.0008&lt;/strong&gt; 언저리다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;플래시율 = 엔탈피 차 ÷ 기화열&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13668,7 +13668,7 @@
       </c>
       <c r="AI98" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;유량계의 분류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;차압식은 「관을 좁혀 압력차를 만들고 그 차를 읽는」&lt;/strong&gt; 것이다 — &lt;strong&gt;로타미터는 관이 위로 갈수록 넓어지고 부표가 뜨는 자리로 읽으므로 압력차가 일정&lt;/strong&gt; 하다. &lt;strong&gt;그래서 「가변면적식」&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;로타미터는 면적식&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;유량계의 분류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;차압식은 「관을 좁혀 압력차를 만들고 그 차를 읽는」&lt;/strong&gt; 것이다 — &lt;strong&gt;로타미터는 관이 위로 갈수록 넓어지고 부표가 뜨는 자리로 읽으므로 압력차가 일정&lt;/strong&gt;하다. &lt;strong&gt;그래서 「가변면적식」&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;로타미터는 면적식&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13908,7 +13908,7 @@
       </c>
       <c r="AG100" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;액화시안화수소&lt;/strong&gt;다. &lt;strong&gt;스스로 중합하며 큰 열을 내고 끝내 폭발&lt;/strong&gt; 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;중합반응과 중합방지제&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;중합반응&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작은 분자가 서로 이어져 큰 분자가 되는 반응&lt;/u&gt; — 발열반응&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;중합하기 쉬운 물질&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시안화수소 · 산화에틸렌 · 스티렌 · 아크릴로니트릴 · 비닐아세틸렌&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;열이 쌓여 반응폭주로 이어진다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대책&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;중합방지제(안정제)를 넣고 저온에 저장&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;시안화수소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;황산 등 안정제를 넣어 저장하고 60일마다 순도를 확인&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;액화시안화수소&lt;/strong&gt;다. &lt;strong&gt;스스로 중합하며 큰 열을 내고 끝내 폭발&lt;/strong&gt;한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;중합반응과 중합방지제&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;중합반응&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작은 분자가 서로 이어져 큰 분자가 되는 반응&lt;/u&gt; — 발열반응&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;중합하기 쉬운 물질&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시안화수소 · 산화에틸렌 · 스티렌 · 아크릴로니트릴 · 비닐아세틸렌&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;열이 쌓여 반응폭주로 이어진다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대책&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;중합방지제(안정제)를 넣고 저온에 저장&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;시안화수소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;황산 등 안정제를 넣어 저장하고 60일마다 순도를 확인&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH100" s="32" t="inlineStr">
@@ -13918,7 +13918,7 @@
       </c>
       <c r="AI100" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;중합반응의 위험&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;중합은 「사슬이 이어지며 열을 내는」 반응&lt;/strong&gt;이라 &lt;strong&gt;한번 시작되면 열이 열을 불러 폭주&lt;/strong&gt; 한다. &lt;strong&gt;시안화수소 · 산화에틸렌 · 스티렌&lt;/strong&gt; 세 이름을 붙들어 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;액화시안화수소는 중합 발열&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;중합반응의 위험&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;중합은 「사슬이 이어지며 열을 내는」 반응&lt;/strong&gt;이라 &lt;strong&gt;한번 시작되면 열이 열을 불러 폭주&lt;/strong&gt;한다. &lt;strong&gt;시안화수소 · 산화에틸렌 · 스티렌&lt;/strong&gt; 세 이름을 붙들어 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;액화시안화수소는 중합 발열&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14003,7 +14003,7 @@
       </c>
       <c r="U101" s="32" t="inlineStr">
         <is>
-          <t>25℃ 액화프로판가스 용기에 10kg 의 LPG가 들어있다. 용기가 파열되어 대기압으로 되었다고 한다. 파열되는 순간 증발되는 프로판의 질량은 약 얼마인가? (단, LPG의 비열은 2.4kJ/kg.℃이고, 표준비점은 -42.2℃ 증발잠열은 384.2kJ/kg이라고 한다.)</t>
+          <t>25℃ 액화프로판가스 용기에 10kg의 LPG가 들어있다. 용기가 파열되어 대기압으로 되었다고 한다. 파열되는 순간 증발되는 프로판의 질량은 약 얼마인가? (단, LPG의 비열은 2.4kJ/kg.℃이고, 표준비점은 -42.2℃ 증발잠열은 384.2kJ/kg이라고 한다.)</t>
         </is>
       </c>
       <c r="V101" s="32" t="inlineStr"/>
@@ -14037,12 +14037,12 @@
       </c>
       <c r="AG101" s="32" t="inlineStr">
         <is>
-          <t>식힐 열은 $10 \times 2.4 \times ( 25 + 42.2 ) = 1 {,} 612.8$ [kJ] 다. $\dfrac{1 {,} 612.8}{384.2} \fallingdotseq 4.20$ [kg] 이 증발한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;파열 순간의 증발량&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;셈&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;① 온도차&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;25 − (−42.2) = 67.2 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;끓는점까지 내려가야 한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;② 방출열&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 × 2.4 × 67.2 = 1,612.8 [kJ]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;현열&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;③ 증발량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1,612.8 ÷ 384.2 = 4.20 [kg]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;잠열로 나눈다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;뜻&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;남은 액이 스스로 식으며 그만큼 증발한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;BLEVE 의 바탕&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>식힐 열은 $10 \times 2.4 \times ( 25 + 42.2 ) = 1 {,} 612.8$ [kJ]다. $\dfrac{1 {,} 612.8}{384.2} \fallingdotseq 4.20$ [kg]이 증발한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;파열 순간의 증발량&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;셈&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;① 온도차&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;25 − (−42.2) = 67.2 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;끓는점까지 내려가야 한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;② 방출열&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 × 2.4 × 67.2 = 1,612.8 [kJ]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;현열&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;③ 증발량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1,612.8 ÷ 384.2 = 4.20 [kg]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;잠열로 나눈다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;뜻&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;남은 액이 스스로 식으며 그만큼 증발한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;BLEVE의 바탕&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH101" s="32" t="inlineStr">
         <is>
-          <t>① 0.42 [kg] 은 자릿수가 한 자리 어긋난다.&lt;br&gt;② 0.52 [kg] 도 맞지 않는다.&lt;br&gt;④ 7.62 [kg] 도 그렇다.</t>
+          <t>① 0.42 [kg]은 자릿수가 한 자리 어긋난다.&lt;br&gt;② 0.52 [kg] 도 맞지 않는다.&lt;br&gt;④ 7.62 [kg] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI101" s="32" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="AG103" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;너비 1.2 [m] 이상&lt;/strong&gt;의 계단참을 둔다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;계단의 설치기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;매 [m²] 당 500 [kg] 이상의 하중에 견딜 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;안전율 4 이상&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;폭&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;급유용·보수용 등은 예외&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;계단참&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높이 3 [m] 를 넘으면 3 [m] 이내마다 너비 1.2 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;난간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높이 1 [m] 이상이면 개방된 쪽에 안전난간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;유효높이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2 [m] 이내에 장애물이 없을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;너비 1.2 [m] 이상&lt;/strong&gt;의 계단참을 둔다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;계단의 설치기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;매 [m²] 당 500 [kg] 이상의 하중에 견딜 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;안전율 4 이상&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;폭&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;급유용·보수용 등은 예외&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;계단참&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높이 3 [m]를 넘으면 3 [m] 이내마다 너비 1.2 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;난간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높이 1 [m] 이상이면 개방된 쪽에 안전난간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;유효높이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2 [m] 이내에 장애물이 없을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH103" s="32" t="inlineStr">
         <is>
-          <t>① 3.5 [m] 는 기준값이 아니다.&lt;br&gt;② 2.5 [m] 도 그렇다.&lt;br&gt;④ 1.0 [m] 는 계단의 폭 기준이다.</t>
+          <t>① 3.5 [m]는 기준값이 아니다.&lt;br&gt;② 2.5 [m] 도 그렇다.&lt;br&gt;④ 1.0 [m]는 계단의 폭 기준이다.</t>
         </is>
       </c>
       <c r="AI103" s="32" t="inlineStr">
@@ -14433,12 +14433,12 @@
       </c>
       <c r="AH104" s="32" t="inlineStr">
         <is>
-          <t>① 2분의 1 은 기준값이 아니다.&lt;br&gt;③ 4분의 1 도 그렇다.&lt;br&gt;④ 5분의 1 도 그렇다.</t>
+          <t>① 2분의 1은 기준값이 아니다.&lt;br&gt;③ 4분의 1 도 그렇다.&lt;br&gt;④ 5분의 1 도 그렇다.</t>
         </is>
       </c>
       <c r="AI104" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;시스템 비계의 구조&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;받침철물에 수직재가 얕게 얹히면 흔들리다 빠진다&lt;/strong&gt; — &lt;strong&gt;전체길이의 1/3 은 「빠지지 않을 만큼」 물리라는 뜻&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;겹침길이는 받침철물의 1/3 이상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;시스템 비계의 구조&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;받침철물에 수직재가 얕게 얹히면 흔들리다 빠진다&lt;/strong&gt; — &lt;strong&gt;전체길이의 1/3은 「빠지지 않을 만큼」 물리라는 뜻&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;겹침길이는 받침철물의 1/3 이상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14700,7 +14700,7 @@
       </c>
       <c r="AI106" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;통나무 비계&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「4층 · 12 [m]」&lt;/strong&gt; 한 짝이다 — &lt;strong&gt;한 층을 3 [m] 로 보면 4층이 곧 12 [m]&lt;/strong&gt;라 앞뒤가 맞는다. &lt;strong&gt;그보다 높은 건물에는 강관비계&lt;/strong&gt;를 쓴다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;통나무 비계는 4층 · 12 [m] 이하&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;통나무 비계&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「4층 · 12 [m]」&lt;/strong&gt;한 짝이다 — &lt;strong&gt;한 층을 3 [m]로 보면 4층이 곧 12 [m]&lt;/strong&gt;라 앞뒤가 맞는다. &lt;strong&gt;그보다 높은 건물에는 강관비계&lt;/strong&gt;를 쓴다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;통나무 비계는 4층 · 12 [m] 이하&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -15335,7 +15335,7 @@
       </c>
       <c r="AG111" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;최고속도가 시속 10 [km] 이하&lt;/strong&gt;인 기계는 제한속도를 따로 정하지 않아도 된다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;차량계 건설기계의 속도 관련 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;제한속도를 정해야 하는 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;최고속도가 시속 10 [km] 를 넘는 기계&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정하지 않아도 되는 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;최고속도가 시속 10 [km] 이하인 기계&lt;/u&gt; — 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;누가 정하나&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사업주가 작업장소의 지형과 지반 상태에 맞게&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;운전자는&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정해진 제한속도를 지켜야 한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;최고속도가 시속 10 [km] 이하&lt;/strong&gt;인 기계는 제한속도를 따로 정하지 않아도 된다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;차량계 건설기계의 속도 관련 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;제한속도를 정해야 하는 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;최고속도가 시속 10 [km]를 넘는 기계&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정하지 않아도 되는 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;최고속도가 시속 10 [km] 이하인 기계&lt;/u&gt; — 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;누가 정하나&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사업주가 작업장소의 지형과 지반 상태에 맞게&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;운전자는&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정해진 제한속도를 지켜야 한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH111" s="32" t="inlineStr">
@@ -15345,7 +15345,7 @@
       </c>
       <c r="AI111" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;차량계 건설기계의 제한속도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;시속 10 [km] 는 사람이 뛰는 속도 남짓&lt;/strong&gt;이다 — &lt;strong&gt;그보다 느리면 부딪쳐도 크게 다치지 않으므로 따로 제한을 걸지 않는다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;시속 10 [km] 이하면 면제&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;차량계 건설기계의 제한속도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;시속 10 [km]는 사람이 뛰는 속도 남짓&lt;/strong&gt;이다 — &lt;strong&gt;그보다 느리면 부딪쳐도 크게 다치지 않으므로 따로 제한을 걸지 않는다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;시속 10 [km] 이하면 면제&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -15856,12 +15856,12 @@
       </c>
       <c r="AH115" s="32" t="inlineStr">
         <is>
-          <t>① 30 [cm] 는 기준에 못 미친다.&lt;br&gt;③ 50 [cm] 는 기준보다 넓다.&lt;br&gt;④ 60 [cm] 도 그렇다.</t>
+          <t>① 30 [cm]는 기준에 못 미친다.&lt;br&gt;③ 50 [cm]는 기준보다 넓다.&lt;br&gt;④ 60 [cm] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI115" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;달비계의 구조&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;작업발판의 폭 40 [cm] 는 비계 일반과 같은 값&lt;/strong&gt;이다 — &lt;strong&gt;다만 달비계는 「틈이 없도록」&lt;/strong&gt;이라는 조건이 더 붙는다. &lt;strong&gt;비계 조립·해체 때의 20 [cm] 와는 다른 자리&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;달비계 작업발판은 40 [cm] 이상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;달비계의 구조&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;작업발판의 폭 40 [cm]는 비계 일반과 같은 값&lt;/strong&gt;이다 — &lt;strong&gt;다만 달비계는 「틈이 없도록」&lt;/strong&gt;이라는 조건이 더 붙는다. &lt;strong&gt;비계 조립·해체 때의 20 [cm] 와는 다른 자리&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;달비계 작업발판은 40 [cm] 이상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -15980,12 +15980,12 @@
       </c>
       <c r="AG116" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;강설량 시간당 1 [cm] 이상&lt;/strong&gt;이면 멈춘다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;철골작업의 중지기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;풍속&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;초당 10 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강우량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시간당 1 [mm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;[cm] 가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강설량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시간당 1 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기온&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;중지기준에 없다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;강설량 시간당 1 [cm] 이상&lt;/strong&gt;이면 멈춘다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;철골작업의 중지기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;풍속&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;초당 10 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강우량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시간당 1 [mm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;[cm]가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강설량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시간당 1 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기온&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;중지기준에 없다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH116" s="32" t="inlineStr">
         <is>
-          <t>① 풍속은 초당 1 [m] 가 아니라 10 [m] 이상이다.&lt;br&gt;② 강우량은 시간당 1 [cm] 가 아니라 1 [mm] 이상이다.&lt;br&gt;④ 10분간 평균풍속 초당 5 [m] 는 기준이 아니다.</t>
+          <t>① 풍속은 초당 1 [m]가 아니라 10 [m] 이상이다.&lt;br&gt;② 강우량은 시간당 1 [cm]가 아니라 1 [mm] 이상이다.&lt;br&gt;④ 10분간 평균풍속 초당 5 [m]는 기준이 아니다.</t>
         </is>
       </c>
       <c r="AI116" s="32" t="inlineStr">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="AI117" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;PC말뚝의 절단&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;PC 는 「미리(Pre) 눌러(Stressed) 둔 콘크리트」&lt;/strong&gt;다 — &lt;strong&gt;그 힘이 말뚝 전체에 걸려 있어 한 곳을 자르면 균형이 깨진다&lt;/strong&gt;. &lt;strong&gt;그래서 PC말뚝은 길이를 미리 맞춰 주문&lt;/strong&gt; 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;PC말뚝은 자르면 안 된다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;PC말뚝의 절단&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;PC는 「미리(Pre) 눌러(Stressed) 둔 콘크리트」&lt;/strong&gt;다 — &lt;strong&gt;그 힘이 말뚝 전체에 걸려 있어 한 곳을 자르면 균형이 깨진다&lt;/strong&gt;. &lt;strong&gt;그래서 PC말뚝은 길이를 미리 맞춰 주문&lt;/strong&gt;한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;PC말뚝은 자르면 안 된다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
